--- a/raw/20260305_r6_SG_Prioscout_NorCWD_RT-QuIC.xlsx
+++ b/raw/20260305_r6_SG_Prioscout_NorCWD_RT-QuIC.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MNPRO\Desktop\RT-QuIC Data\Sarah's RT-QuIC Data\2026\20260305_r6_SG_Prioscout_NorCWD_RT-QuIC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rowde002\Documents\Projects\canadian-reindeer-sentinels\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E032FBFE-DA8E-42A6-9A4E-E5F4DAC42141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2A3CD53-7383-4A9C-952F-D966F9100657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{6EED0C16-43E5-4541-A1CF-8FB94ECC6770}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6EED0C16-43E5-4541-A1CF-8FB94ECC6770}"/>
   </bookViews>
   <sheets>
     <sheet name="Microplate Cycle 1 (0 h)" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="51">
   <si>
     <t>User: USER</t>
   </si>
@@ -190,6 +190,9 @@
   </si>
   <si>
     <t>3. Dilutions</t>
+  </si>
+  <si>
+    <t>S-2205</t>
   </si>
 </sst>
 </file>
@@ -1207,7 +1210,7 @@
         <v>36</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D31" s="14"/>
       <c r="E31" s="14"/>
@@ -1228,7 +1231,7 @@
         <v>36</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D32" s="14"/>
       <c r="E32" s="14"/>
@@ -1249,7 +1252,7 @@
         <v>36</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D33" s="14"/>
       <c r="E33" s="14"/>
@@ -1269,8 +1272,8 @@
       <c r="B34" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C34" s="17" t="s">
-        <v>37</v>
+      <c r="C34" s="14" t="s">
+        <v>50</v>
       </c>
       <c r="D34" s="17"/>
       <c r="E34" s="17"/>
